--- a/data/trans_dic/P25A$molestias-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25A$molestias-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, las molestias por causa del tabaco</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, las molestias por causa del tabaco (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,56; 29,49</t>
+          <t>8,24; 30,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,63; 17,59</t>
+          <t>4,58; 17,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,51; 34,72</t>
+          <t>15,36; 34,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,33</t>
+          <t>0,0; 26,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,6; 41,14</t>
+          <t>10,25; 42,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,49; 35,95</t>
+          <t>12,23; 34,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,95; 23,16</t>
+          <t>7,27; 23,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,98; 21,78</t>
+          <t>7,86; 21,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,4; 31,5</t>
+          <t>16,07; 30,96</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 18,53</t>
+          <t>7,08; 18,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 16,69</t>
+          <t>3,41; 16,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,34; 35,9</t>
+          <t>15,56; 35,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 29,91</t>
+          <t>3,66; 26,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,0</t>
+          <t>0,0; 11,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 35,16</t>
+          <t>4,96; 34,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,99; 17,08</t>
+          <t>7,11; 17,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 12,04</t>
+          <t>2,99; 12,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,92; 31,52</t>
+          <t>14,68; 31,98</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,75; 28,09</t>
+          <t>8,75; 27,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,79; 19,39</t>
+          <t>5,56; 18,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,79</t>
+          <t>1,18; 11,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,63</t>
+          <t>0,0; 13,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 26,99</t>
+          <t>3,12; 28,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,65; 22,77</t>
+          <t>6,96; 22,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,41; 15,48</t>
+          <t>4,36; 14,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 12,11</t>
+          <t>2,52; 12,1</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,17; 33,5</t>
+          <t>14,74; 35,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 14,73</t>
+          <t>4,05; 15,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,15; 17,97</t>
+          <t>4,27; 18,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,84; 37,69</t>
+          <t>12,15; 39,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 20,21</t>
+          <t>2,2; 20,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 22,11</t>
+          <t>3,9; 22,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,52; 32,35</t>
+          <t>16,19; 32,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 13,56</t>
+          <t>4,26; 13,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,6; 16,78</t>
+          <t>5,03; 15,72</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,13</t>
+          <t>0,0; 14,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,71; 29,12</t>
+          <t>6,86; 28,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,86; 35,02</t>
+          <t>5,23; 32,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,3</t>
+          <t>0,0; 17,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,14; 38,55</t>
+          <t>6,94; 36,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,55; 61,75</t>
+          <t>14,7; 64,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 11,03</t>
+          <t>1,23; 10,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,95; 26,05</t>
+          <t>8,81; 26,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,3; 38,78</t>
+          <t>13,06; 37,4</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,93; 44,0</t>
+          <t>19,99; 44,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,57; 15,65</t>
+          <t>3,66; 16,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,18; 34,41</t>
+          <t>9,64; 34,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,28; 40,2</t>
+          <t>5,34; 43,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,87; 39,47</t>
+          <t>18,48; 37,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,77; 12,53</t>
+          <t>2,91; 12,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,8; 25,8</t>
+          <t>7,73; 24,78</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,48; 35,87</t>
+          <t>17,42; 35,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,5; 17,33</t>
+          <t>6,83; 17,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,09; 26,51</t>
+          <t>12,3; 26,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,0; 41,25</t>
+          <t>11,5; 39,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 14,26</t>
+          <t>1,46; 13,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,06; 19,07</t>
+          <t>5,3; 19,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,02; 32,94</t>
+          <t>18,02; 33,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,82; 13,28</t>
+          <t>5,96; 13,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,12; 21,48</t>
+          <t>11,24; 21,4</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,29; 26,27</t>
+          <t>13,14; 26,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,52; 22,17</t>
+          <t>8,22; 21,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,72; 16,45</t>
+          <t>4,82; 16,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,75; 26,46</t>
+          <t>8,71; 26,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,96; 22,36</t>
+          <t>4,91; 22,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,2; 20,17</t>
+          <t>3,14; 19,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,06; 23,97</t>
+          <t>13,21; 23,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,73; 18,76</t>
+          <t>8,96; 19,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,33; 14,89</t>
+          <t>5,18; 15,35</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,74; 21,93</t>
+          <t>15,98; 22,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,52; 13,2</t>
+          <t>8,56; 12,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,12; 19,28</t>
+          <t>12,97; 19,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,4; 19,27</t>
+          <t>10,33; 18,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,35; 12,83</t>
+          <t>6,18; 12,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,28; 17,63</t>
+          <t>10,23; 17,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,25; 20,38</t>
+          <t>15,15; 20,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,33; 11,93</t>
+          <t>8,35; 12,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,69; 17,37</t>
+          <t>12,52; 17,33</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, las molestias por causa del tabaco</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, las molestias por causa del tabaco (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4440; 13699</t>
+          <t>3827; 14272</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3752; 14269</t>
+          <t>3718; 14448</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12249; 27413</t>
+          <t>12131; 27292</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4884</t>
+          <t>0; 5336</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3843; 16470</t>
+          <t>4104; 16892</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6492; 18687</t>
+          <t>6356; 17930</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4622; 15405</t>
+          <t>4833; 15904</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9668; 26381</t>
+          <t>9523; 25652</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21470; 41244</t>
+          <t>21037; 40537</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7795; 21097</t>
+          <t>8055; 20852</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4086; 20188</t>
+          <t>4127; 19580</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11817; 25968</t>
+          <t>11252; 25924</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>942; 7732</t>
+          <t>947; 6834</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5980</t>
+          <t>0; 6865</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1474; 10299</t>
+          <t>1454; 10099</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9765; 23865</t>
+          <t>9932; 24614</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5177; 21767</t>
+          <t>5398; 22661</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15166; 32035</t>
+          <t>14913; 32496</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4941; 17901</t>
+          <t>5576; 17722</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4764; 15955</t>
+          <t>4576; 15609</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>723; 6692</t>
+          <t>730; 7225</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1795</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5779</t>
+          <t>0; 4262</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>878; 7453</t>
+          <t>860; 7830</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5185; 17755</t>
+          <t>5430; 17609</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5077; 17811</t>
+          <t>5014; 16586</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1881; 10856</t>
+          <t>2261; 10846</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10750; 25421</t>
+          <t>11186; 26852</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4157; 15527</t>
+          <t>4271; 16782</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3613; 15650</t>
+          <t>3723; 15867</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4084; 14204</t>
+          <t>4578; 14939</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>997; 9396</t>
+          <t>1022; 9452</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1771; 9875</t>
+          <t>1741; 9893</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18757; 36737</t>
+          <t>18383; 36506</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6876; 20605</t>
+          <t>6471; 20835</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7378; 22111</t>
+          <t>6622; 20718</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5398</t>
+          <t>0; 5972</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3385; 14682</t>
+          <t>3457; 14349</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1859; 11110</t>
+          <t>1658; 10210</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 5893</t>
+          <t>0; 5123</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1916; 10352</t>
+          <t>1864; 9813</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2998; 10551</t>
+          <t>2511; 10934</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>861; 7738</t>
+          <t>862; 7621</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6912; 20131</t>
+          <t>6808; 20493</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6491; 18931</t>
+          <t>6374; 18255</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10538; 23263</t>
+          <t>10569; 23573</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2969; 13010</t>
+          <t>3040; 13508</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4518; 15268</t>
+          <t>4279; 15159</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>993; 7563</t>
+          <t>1004; 8238</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1888</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1770</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13526; 28291</t>
+          <t>13244; 26924</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2905; 13152</t>
+          <t>3050; 13259</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4774; 15780</t>
+          <t>4727; 15158</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16111; 33056</t>
+          <t>16054; 32890</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10565; 28162</t>
+          <t>11104; 28105</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15343; 33639</t>
+          <t>15612; 33736</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2959; 13558</t>
+          <t>3780; 12971</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1809; 13091</t>
+          <t>1343; 12000</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4272; 16105</t>
+          <t>4475; 16563</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22524; 41188</t>
+          <t>22528; 42096</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>14799; 33785</t>
+          <t>15172; 34698</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>23493; 45392</t>
+          <t>23758; 45221</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>18404; 36387</t>
+          <t>18196; 36255</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11096; 28875</t>
+          <t>10708; 27822</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4822; 16793</t>
+          <t>4922; 17283</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6314; 19098</t>
+          <t>6284; 18955</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3318; 14964</t>
+          <t>3287; 15013</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2049; 12895</t>
+          <t>2008; 12399</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>27512; 50505</t>
+          <t>27827; 49808</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>17210; 36991</t>
+          <t>17660; 38106</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8844; 24724</t>
+          <t>8609; 25492</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>98278; 136992</t>
+          <t>99837; 137503</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>69519; 107720</t>
+          <t>69852; 104258</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>79415; 116761</t>
+          <t>78537; 115709</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26066; 48311</t>
+          <t>25904; 47492</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>24537; 49587</t>
+          <t>23883; 48479</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34529; 59203</t>
+          <t>34350; 59179</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>133501; 178395</t>
+          <t>132571; 176070</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>100155; 143504</t>
+          <t>100440; 145462</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>119428; 163504</t>
+          <t>117851; 163134</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$molestias-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25A$molestias-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,24; 30,73</t>
+          <t>9,58; 30,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 17,81</t>
+          <t>4,78; 18,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,36; 34,56</t>
+          <t>15,74; 36,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,58</t>
+          <t>0,0; 21,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,25; 42,19</t>
+          <t>9,79; 40,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,23; 34,49</t>
+          <t>12,31; 35,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,27; 23,91</t>
+          <t>6,92; 23,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,86; 21,18</t>
+          <t>7,74; 21,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,07; 30,96</t>
+          <t>16,57; 31,13</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,08; 18,32</t>
+          <t>6,68; 19,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,41; 16,19</t>
+          <t>3,48; 16,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,56; 35,84</t>
+          <t>16,33; 36,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 26,43</t>
+          <t>3,69; 30,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,48</t>
+          <t>0,0; 11,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 34,48</t>
+          <t>4,05; 37,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,11; 17,62</t>
+          <t>6,94; 17,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 12,54</t>
+          <t>2,84; 11,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,68; 31,98</t>
+          <t>15,01; 31,49</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,75; 27,8</t>
+          <t>7,73; 26,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,56; 18,97</t>
+          <t>5,85; 18,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,65</t>
+          <t>1,19; 11,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,27 +918,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,0</t>
+          <t>0,0; 14,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 28,36</t>
+          <t>3,22; 28,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,96; 22,58</t>
+          <t>6,67; 22,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 14,41</t>
+          <t>4,36; 15,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 12,1</t>
+          <t>2,36; 12,41</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,74; 35,39</t>
+          <t>14,45; 33,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 15,92</t>
+          <t>4,02; 15,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,27; 18,22</t>
+          <t>4,08; 17,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,15; 39,65</t>
+          <t>11,03; 37,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 20,33</t>
+          <t>1,99; 19,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,9; 22,15</t>
+          <t>3,85; 21,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,19; 32,15</t>
+          <t>15,8; 31,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 13,71</t>
+          <t>4,67; 14,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,03; 15,72</t>
+          <t>5,67; 15,66</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,53</t>
+          <t>0,0; 15,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,86; 28,46</t>
+          <t>6,41; 28,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 32,18</t>
+          <t>5,64; 33,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,65</t>
+          <t>0,0; 15,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,94; 36,54</t>
+          <t>7,0; 36,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,7; 64,0</t>
+          <t>17,17; 63,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 10,87</t>
+          <t>1,22; 10,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,81; 26,52</t>
+          <t>8,76; 26,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,06; 37,4</t>
+          <t>12,42; 38,9</t>
         </is>
       </c>
     </row>
@@ -1228,22 +1228,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,99; 44,59</t>
+          <t>20,13; 46,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,66; 16,25</t>
+          <t>3,57; 16,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,64; 34,16</t>
+          <t>10,28; 33,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,34; 43,79</t>
+          <t>5,34; 40,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1258,17 +1258,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,48; 37,56</t>
+          <t>18,21; 39,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,91; 12,63</t>
+          <t>2,9; 12,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,73; 24,78</t>
+          <t>7,71; 25,53</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,42; 35,69</t>
+          <t>17,6; 35,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,83; 17,29</t>
+          <t>6,74; 17,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,3; 26,58</t>
+          <t>11,95; 26,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,5; 39,46</t>
+          <t>11,57; 39,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,07</t>
+          <t>1,91; 15,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,3; 19,62</t>
+          <t>5,25; 19,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,02; 33,67</t>
+          <t>18,17; 33,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,96; 13,64</t>
+          <t>5,94; 14,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,24; 21,4</t>
+          <t>10,52; 21,2</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,14; 26,17</t>
+          <t>13,36; 25,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,22; 21,36</t>
+          <t>8,46; 22,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,82; 16,93</t>
+          <t>5,02; 15,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,71; 26,26</t>
+          <t>8,82; 26,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,91; 22,43</t>
+          <t>6,05; 22,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,14; 19,39</t>
+          <t>3,31; 19,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,21; 23,64</t>
+          <t>13,43; 23,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,96; 19,33</t>
+          <t>9,17; 19,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,18; 15,35</t>
+          <t>5,38; 14,52</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,98; 22,02</t>
+          <t>15,9; 22,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,56; 12,78</t>
+          <t>8,59; 12,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,97; 19,11</t>
+          <t>12,8; 19,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,33; 18,94</t>
+          <t>10,68; 19,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,18; 12,54</t>
+          <t>5,96; 12,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,23; 17,62</t>
+          <t>10,05; 17,52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,15; 20,12</t>
+          <t>15,24; 20,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,35; 12,1</t>
+          <t>8,31; 11,98</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,52; 17,33</t>
+          <t>12,82; 17,48</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3827; 14272</t>
+          <t>4449; 13970</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3718; 14448</t>
+          <t>3874; 14626</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12131; 27292</t>
+          <t>12429; 28479</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5336</t>
+          <t>0; 4354</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4104; 16892</t>
+          <t>3921; 16365</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6356; 17930</t>
+          <t>6397; 18645</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4833; 15904</t>
+          <t>4605; 15587</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9523; 25652</t>
+          <t>9371; 26565</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21037; 40537</t>
+          <t>21693; 40768</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8055; 20852</t>
+          <t>7610; 21852</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4127; 19580</t>
+          <t>4207; 20251</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11252; 25924</t>
+          <t>11810; 26672</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>947; 6834</t>
+          <t>954; 7819</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6865</t>
+          <t>0; 6905</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1454; 10099</t>
+          <t>1188; 11033</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9932; 24614</t>
+          <t>9696; 24697</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5398; 22661</t>
+          <t>5132; 20764</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14913; 32496</t>
+          <t>15254; 32003</t>
         </is>
       </c>
     </row>
@@ -2187,17 +2187,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5576; 17722</t>
+          <t>4927; 17150</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4576; 15609</t>
+          <t>4817; 15396</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>730; 7225</t>
+          <t>741; 7212</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2207,27 +2207,27 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4262</t>
+          <t>0; 4845</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>860; 7830</t>
+          <t>888; 7894</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5430; 17609</t>
+          <t>5203; 17451</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5014; 16586</t>
+          <t>5018; 17738</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2261; 10846</t>
+          <t>2111; 11118</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11186; 26852</t>
+          <t>10965; 25490</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4271; 16782</t>
+          <t>4236; 15909</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3723; 15867</t>
+          <t>3550; 15422</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4578; 14939</t>
+          <t>4155; 14292</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1022; 9452</t>
+          <t>926; 9124</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1741; 9893</t>
+          <t>1721; 9440</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18383; 36506</t>
+          <t>17945; 35604</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6471; 20835</t>
+          <t>7100; 21387</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6622; 20718</t>
+          <t>7464; 20636</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5972</t>
+          <t>0; 6168</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3457; 14349</t>
+          <t>3231; 14261</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1658; 10210</t>
+          <t>1788; 10655</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 5123</t>
+          <t>0; 4547</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1864; 9813</t>
+          <t>1879; 9888</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2511; 10934</t>
+          <t>2933; 10785</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>862; 7621</t>
+          <t>855; 7679</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6808; 20493</t>
+          <t>6773; 20762</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6374; 18255</t>
+          <t>6061; 18990</t>
         </is>
       </c>
     </row>
@@ -2676,22 +2676,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10569; 23573</t>
+          <t>10641; 24352</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3040; 13508</t>
+          <t>2968; 13427</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4279; 15159</t>
+          <t>4560; 14900</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1004; 8238</t>
+          <t>1004; 7605</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2706,17 +2706,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13244; 26924</t>
+          <t>13053; 28403</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3050; 13259</t>
+          <t>3046; 13505</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4727; 15158</t>
+          <t>4714; 15619</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16054; 32890</t>
+          <t>16219; 32424</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11104; 28105</t>
+          <t>10951; 28502</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15612; 33736</t>
+          <t>15164; 34157</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3780; 12971</t>
+          <t>3802; 13141</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1343; 12000</t>
+          <t>1751; 14154</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4475; 16563</t>
+          <t>4436; 16115</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22528; 42096</t>
+          <t>22718; 41961</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>15172; 34698</t>
+          <t>15097; 35822</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>23758; 45221</t>
+          <t>22239; 44810</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>18196; 36255</t>
+          <t>18512; 35984</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>10708; 27822</t>
+          <t>11019; 28777</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4922; 17283</t>
+          <t>5124; 16259</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6284; 18955</t>
+          <t>6364; 19479</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3287; 15013</t>
+          <t>4048; 14852</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2008; 12399</t>
+          <t>2115; 12312</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>27827; 49808</t>
+          <t>28288; 49897</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>17660; 38106</t>
+          <t>18076; 38088</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8609; 25492</t>
+          <t>8941; 24105</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>99837; 137503</t>
+          <t>99299; 139156</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>69852; 104258</t>
+          <t>70060; 105400</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>78537; 115709</t>
+          <t>77530; 115363</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25904; 47492</t>
+          <t>26767; 48486</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>23883; 48479</t>
+          <t>23031; 48870</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34350; 59179</t>
+          <t>33752; 58845</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>132571; 176070</t>
+          <t>133355; 177937</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>100440; 145462</t>
+          <t>99887; 144016</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>117851; 163134</t>
+          <t>120630; 164544</t>
         </is>
       </c>
     </row>
